--- a/data/gravel/Tanglefoot Hardtack V2 2025.xlsx
+++ b/data/gravel/Tanglefoot Hardtack V2 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1606833-4BCB-B64D-8CA7-2B22C62D5FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1449691-73D6-6942-B3AE-3FABB4019F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31460" yWindow="-17860" windowWidth="29780" windowHeight="16900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3940" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -350,9 +350,6 @@
     <t>drop bar</t>
   </si>
   <si>
-    <t>Poultney, Vermont</t>
-  </si>
-  <si>
     <t>https://analogcycles.com/cdn/shop/files/moonshiner-073.jpg?v=1704307954</t>
   </si>
   <si>
@@ -381,6 +378,9 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>Poultney, Vermont, USA</t>
   </si>
 </sst>
 </file>
@@ -812,12 +812,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="22">
@@ -825,7 +825,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -1509,142 +1509,124 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
         <v>44</v>
       </c>
-      <c r="B56">
-        <v>180</v>
+      <c r="B56" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
         <v>45</v>
       </c>
-      <c r="B57">
-        <v>180</v>
-      </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
         <v>46</v>
       </c>
+      <c r="B58">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
         <v>47</v>
       </c>
+      <c r="B59" s="1" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>82</v>
-      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
         <v>49</v>
       </c>
-      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
         <v>50</v>
       </c>
+      <c r="B62">
+        <v>180</v>
+      </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
         <v>51</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
         <v>52</v>
       </c>
-      <c r="B64">
-        <v>1</v>
-      </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
         <v>53</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
         <v>54</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>34</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
         <v>55</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="B67" s="1"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
         <v>56</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>34</v>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1652,45 +1634,56 @@
         <v>58</v>
       </c>
       <c r="B70">
-        <v>1080</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
         <v>59</v>
       </c>
+      <c r="B71" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
         <v>60</v>
       </c>
-      <c r="B72" s="1"/>
+      <c r="B72" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
         <v>61</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
         <v>62</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>105</v>
+      <c r="B74" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
         <v>63</v>
       </c>
+      <c r="B75" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
         <v>64</v>
       </c>
+      <c r="B76">
+        <v>1080</v>
+      </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
@@ -1701,15 +1694,22 @@
       <c r="A78" t="s">
         <v>66</v>
       </c>
+      <c r="B78" s="1"/>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
         <v>67</v>
       </c>
+      <c r="B79" s="1" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
         <v>85</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
